--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{2EC10805-9208-4634-987A-FA3B91D38AD6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025337E5-5D53-47A8-94B8-9CFCF59B9DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="2" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
-    <sheet name="BFLU_1Result" r:id="rId3" sheetId="3"/>
+    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
+    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
+    <sheet name="BFLU_1Result" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="129">
   <si>
     <t>Result</t>
   </si>
@@ -269,150 +269,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Thu Jun 18 00:57:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 00:58:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 00:59:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:00:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:01:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:02:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:03:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:04:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:05:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:06:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:07:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:08:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:09:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:10:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:11:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:12:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:12:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:13:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:14:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:15:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:16:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:18:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:19:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:20:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:21:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:22:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:45:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:46:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:47:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:48:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:49:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:50:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:50:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:51:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:52:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:53:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:54:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:55:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:56:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:57:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:58:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:59:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 01:59:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:00:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:01:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:02:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:03:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:04:22 IST 2026</t>
-  </si>
-  <si>
     <t>Payment app+ 1st + 2nd +3rd lookup</t>
   </si>
   <si>
@@ -422,542 +278,163 @@
     <t xml:space="preserve">Payment app+ CAN </t>
   </si>
   <si>
-    <t>Thu Jun 18 20:32:42 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:07:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:08:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:09:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:10:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:11:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:11:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:12:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:13:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:14:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:14:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:15:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:16:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:17:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:18:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:18:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:19:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:20:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:21:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:22:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:22:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:23:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:24:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:24:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:25:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:26:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:27:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:27:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:28:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:29:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:29:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:30:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:31:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:32:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:32:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:33:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:34:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:34:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:35:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:36:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:37:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:38:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:38:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:39:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:40:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:41:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:41:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:42:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:43:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:43:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:33:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:35:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:36:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:37:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:38:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:39:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:40:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:41:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:42:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:43:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:44:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:46:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:46:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:47:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:48:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:49:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:50:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:51:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:52:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:53:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:54:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:55:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:56:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:57:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:58:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 13:58:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:01:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:03:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:04:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:05:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:05:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:06:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:07:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:08:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:09:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:10:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:11:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:11:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:12:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:13:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:14:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:15:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:16:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:17:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:18:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:18:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:19:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:20:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:21:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:22:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:22:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:23:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:24:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:25:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:26:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:27:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:27:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:28:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:29:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:30:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:31:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:32:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:32:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:33:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:34:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:35:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:35:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:36:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:37:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:38:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:39:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:39:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:40:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:41:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 14:42:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:27:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:29:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:29:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:30:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:31:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:32:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:33:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:34:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:34:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:35:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:36:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:38:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:39:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:39:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:40:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:41:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:42:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:43:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:44:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:44:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:45:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:46:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:47:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:48:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:49:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:49:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:50:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:51:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:52:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:53:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:53:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:54:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:55:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:56:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:56:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:57:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:58:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:59:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:59:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:00:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:01:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:02:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:02:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:03:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:04:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:05:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:05:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:06:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 18:07:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:00:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:01:03 IST 2026</t>
+    <t>Thu Oct 15 11:20:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:23:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:26:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:29:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:48:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:51:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 11:57:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:00:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:06:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:09:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:12:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:16:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:19:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:23:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:25:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:27:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:34:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:37:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:40:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:43:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:46:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:50:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 12:54:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:15:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:19:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:22:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:31:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:35:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:45:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:48:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:51:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:55:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 10:58:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:01:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:04:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:06:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:09:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:15:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:18:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:21:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:23:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:27:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 11:30:01 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1016,37 +493,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1063,10 +540,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1101,7 +578,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1153,7 +630,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1264,21 +741,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1295,7 +772,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1367,29 +844,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="18.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="3" width="9.0" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="11.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="18.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9" style="3" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1427,12 +904,12 @@
         <v>66</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>301</v>
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1447,12 +924,12 @@
         <v>50020002</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>302</v>
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -1467,12 +944,12 @@
         <v>40</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>254</v>
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1487,12 +964,12 @@
         <v>42</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>255</v>
+    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1507,12 +984,12 @@
         <v>41</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s" s="3">
-        <v>256</v>
+    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>59</v>
@@ -1527,12 +1004,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s" s="3">
-        <v>257</v>
+    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1547,12 +1024,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s" s="3">
-        <v>258</v>
+    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1567,12 +1044,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s" s="3">
-        <v>259</v>
+    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1602,12 +1079,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s" s="3">
-        <v>260</v>
+    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1625,12 +1102,12 @@
         <v>40</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s" s="3">
-        <v>261</v>
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1648,12 +1125,12 @@
         <v>41</v>
       </c>
     </row>
-    <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s" s="3">
-        <v>262</v>
+    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>39</v>
@@ -1671,12 +1148,12 @@
         <v>42</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s" s="3">
-        <v>263</v>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1694,12 +1171,12 @@
         <v>42</v>
       </c>
     </row>
-    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s" s="3">
-        <v>264</v>
+    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1717,12 +1194,12 @@
         <v>41</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s" s="3">
-        <v>265</v>
+    <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1740,12 +1217,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s" s="3">
-        <v>266</v>
+    <row r="16" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1763,12 +1240,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s" s="3">
-        <v>267</v>
+    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>60</v>
@@ -1786,12 +1263,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s" s="3">
-        <v>268</v>
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1809,12 +1286,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s" s="3">
-        <v>269</v>
+    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1832,12 +1309,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s" s="3">
-        <v>270</v>
+    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>61</v>
@@ -1855,12 +1332,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B21" t="s" s="3">
-        <v>271</v>
+    <row r="21" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>58</v>
@@ -1881,12 +1358,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s" s="3">
-        <v>272</v>
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1904,12 +1381,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s" s="3">
-        <v>273</v>
+    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1927,12 +1404,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s" s="3">
-        <v>274</v>
+    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>62</v>
@@ -1950,12 +1427,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B25" t="s" s="3">
-        <v>275</v>
+    <row r="25" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1973,12 +1450,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B26" t="s" s="3">
-        <v>276</v>
+    <row r="26" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1996,12 +1473,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>277</v>
+    <row r="27" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>63</v>
@@ -2021,32 +1498,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="10.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="30.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="3" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="8.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.81640625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="3" width="13.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.90625" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="8.81640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13" style="3" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2084,12 +1561,12 @@
         <v>8</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s" s="5">
-        <v>279</v>
+    <row r="2" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -2107,12 +1584,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s" s="5">
-        <v>280</v>
+    <row r="3" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -2130,12 +1607,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s" s="5">
-        <v>281</v>
+    <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -2153,12 +1630,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s" s="5">
-        <v>282</v>
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -2176,12 +1653,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s" s="5">
-        <v>283</v>
+    <row r="6" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>43</v>
@@ -2199,12 +1676,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s" s="5">
-        <v>284</v>
+    <row r="7" spans="1:12" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>44</v>
@@ -2222,12 +1699,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s" s="5">
-        <v>285</v>
+    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>45</v>
@@ -2248,12 +1725,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s" s="5">
-        <v>286</v>
+    <row r="9" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>46</v>
@@ -2274,12 +1751,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s" s="5">
-        <v>287</v>
+    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>48</v>
@@ -2300,12 +1777,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s" s="5">
-        <v>288</v>
+    <row r="11" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>47</v>
@@ -2326,12 +1803,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s" s="5">
-        <v>289</v>
+    <row r="12" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>53</v>
@@ -2352,12 +1829,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s" s="5">
-        <v>290</v>
+    <row r="13" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>54</v>
@@ -2378,12 +1855,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s" s="5">
-        <v>291</v>
+    <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>55</v>
@@ -2404,12 +1881,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s" s="5">
-        <v>292</v>
+    <row r="15" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>49</v>
@@ -2430,12 +1907,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s" s="5">
-        <v>293</v>
+    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>50</v>
@@ -2456,12 +1933,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s" s="5">
-        <v>294</v>
+    <row r="17" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>51</v>
@@ -2482,12 +1959,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s" s="5">
-        <v>295</v>
+    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>52</v>
@@ -2508,12 +1985,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s" s="5">
-        <v>296</v>
+    <row r="19" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>68</v>
@@ -2531,12 +2008,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s" s="5">
-        <v>297</v>
+    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>70</v>
@@ -2557,12 +2034,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B21" t="s" s="5">
-        <v>298</v>
+    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>71</v>
@@ -2583,12 +2060,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s" s="5">
-        <v>299</v>
+    <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>72</v>
@@ -2609,12 +2086,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s" s="5">
-        <v>300</v>
+    <row r="23" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>73</v>
@@ -2636,31 +2113,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="17.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="3" width="33.90625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="3" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="25.1796875" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.453125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="10.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="21.453125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.81640625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="14.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="3" width="13.36328125" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="17.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="33.90625" style="3" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="25.1796875" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.453125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.26953125" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.1796875" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.54296875" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.36328125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2695,39 +2172,62 @@
         <v>66</v>
       </c>
     </row>
-    <row ht="25" r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="25" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="C2" s="6" t="s">
-        <v>123</v>
+        <v>75</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I2" s="3">
+        <v>428853</v>
+      </c>
+      <c r="J2" s="3">
+        <v>311785</v>
+      </c>
+      <c r="K2" s="7">
+        <v>935960</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>76</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="K3" s="7"/>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>278</v>
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -2741,6 +2241,6 @@
       <c r="K4" s="7"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>